--- a/research/traditional_assets/database/data/kenya/kenya_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0476</v>
+        <v>0.0969</v>
       </c>
       <c r="E2">
-        <v>0.0392</v>
+        <v>0.142</v>
       </c>
       <c r="F2">
-        <v>0.2275</v>
+        <v>0.143</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001324174878001368</v>
+        <v>0.0009489134761535918</v>
       </c>
       <c r="J2">
-        <v>0.001019776575318268</v>
+        <v>0.0006890208895808835</v>
       </c>
       <c r="K2">
-        <v>1119.4</v>
+        <v>1424</v>
       </c>
       <c r="L2">
-        <v>0.3278659715306661</v>
+        <v>0.3597594866353393</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>299.4939</v>
       </c>
       <c r="N2">
-        <v>0.003555284676723044</v>
+        <v>0.05862428797932938</v>
       </c>
       <c r="O2">
-        <v>0.01876005002680007</v>
+        <v>0.21031875</v>
       </c>
       <c r="P2">
-        <v>21</v>
+        <v>299.4939</v>
       </c>
       <c r="Q2">
-        <v>0.003555284676723044</v>
+        <v>0.05862428797932938</v>
       </c>
       <c r="R2">
-        <v>0.01876005002680007</v>
+        <v>0.21031875</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1259.3</v>
+        <v>1168.4</v>
       </c>
       <c r="V2">
-        <v>0.2131985711141585</v>
+        <v>0.2287078904613698</v>
       </c>
       <c r="W2">
-        <v>0.1488330341113106</v>
+        <v>0.2027765470388421</v>
       </c>
       <c r="X2">
-        <v>0.09084028036856996</v>
+        <v>0.1376182736685</v>
       </c>
       <c r="Y2">
-        <v>0.05799275374274064</v>
+        <v>0.06515827337034208</v>
       </c>
       <c r="Z2">
-        <v>0.4506403489812664</v>
+        <v>0.4554500190354169</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07674115726781204</v>
+        <v>0.1152564125587455</v>
       </c>
       <c r="AC2">
-        <v>-0.07451634901791428</v>
+        <v>-0.1129707522026638</v>
       </c>
       <c r="AD2">
-        <v>2797.9</v>
+        <v>3076.9</v>
       </c>
       <c r="AE2">
-        <v>40.13001065763865</v>
+        <v>26.31505339344426</v>
       </c>
       <c r="AF2">
-        <v>2838.030010657639</v>
+        <v>3103.215053393444</v>
       </c>
       <c r="AG2">
-        <v>1578.730010657639</v>
+        <v>1934.815053393444</v>
       </c>
       <c r="AH2">
-        <v>0.3245417533987659</v>
+        <v>0.3778917625446076</v>
       </c>
       <c r="AI2">
-        <v>0.2804008966874143</v>
+        <v>0.305753093854989</v>
       </c>
       <c r="AJ2">
-        <v>0.2109070565631991</v>
+        <v>0.2746945294681075</v>
       </c>
       <c r="AK2">
-        <v>0.1781454146238536</v>
+        <v>0.215433894931774</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>222.9935442735315</v>
+        <v>341.1575562700964</v>
       </c>
       <c r="AP2">
-        <v>125.8252977331345</v>
+        <v>214.526560970556</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.181</v>
+        <v>0.22</v>
       </c>
       <c r="E3">
-        <v>0.118</v>
+        <v>0.194</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,82 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>78.2</v>
+        <v>137.3</v>
       </c>
       <c r="L3">
-        <v>0.2612763113932509</v>
+        <v>0.3545055512522592</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>57.66250000000001</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1097706072720351</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.4199745083758194</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>57.66250000000001</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1097706072720351</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.4199745083758194</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>61.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1668484187568157</v>
+        <v>0.1620026651437274</v>
       </c>
       <c r="W3">
-        <v>0.1205673758865248</v>
+        <v>0.2027765470388421</v>
       </c>
       <c r="X3">
-        <v>0.07783463109837697</v>
+        <v>0.1191524539314403</v>
       </c>
       <c r="Y3">
-        <v>0.04273274478814784</v>
+        <v>0.08362409310740182</v>
       </c>
       <c r="Z3">
-        <v>0.4212526389866291</v>
+        <v>0.5687224669603524</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07350640026470634</v>
+        <v>0.1113153141329352</v>
       </c>
       <c r="AC3">
-        <v>-0.07350640026470634</v>
+        <v>-0.1113153141329352</v>
       </c>
       <c r="AD3">
-        <v>65.09999999999999</v>
+        <v>132.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>65.09999999999999</v>
+        <v>132.4</v>
       </c>
       <c r="AG3">
-        <v>3.899999999999991</v>
+        <v>47.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1507293354943274</v>
+        <v>0.2013075870457656</v>
       </c>
       <c r="AI3">
-        <v>0.08754706831629908</v>
+        <v>0.1650049850448654</v>
       </c>
       <c r="AJ3">
-        <v>0.01052063663339626</v>
+        <v>0.08260565840027946</v>
       </c>
       <c r="AK3">
-        <v>0.005715123094958956</v>
+        <v>0.06594172591663183</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -838,10 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0159</v>
+        <v>0.0697</v>
       </c>
       <c r="E4">
-        <v>-0.009979999999999999</v>
+        <v>0.136</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,82 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>67.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="L4">
-        <v>0.3013392857142857</v>
+        <v>0.3664596273291925</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>62.7314</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.143550114416476</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.6645275423728814</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>62.7314</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.143550114416476</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.6645275423728814</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>29.4</v>
+        <v>24.3</v>
       </c>
       <c r="V4">
-        <v>0.05981688708036622</v>
+        <v>0.05560640732265446</v>
       </c>
       <c r="W4">
-        <v>0.1460406750324535</v>
+        <v>0.1965847563515202</v>
       </c>
       <c r="X4">
-        <v>0.07737909743122023</v>
+        <v>0.120219804859396</v>
       </c>
       <c r="Y4">
-        <v>0.06866157760123326</v>
+        <v>0.0763649514921242</v>
       </c>
       <c r="Z4">
-        <v>0.4096561814191661</v>
+        <v>0.4839376291564907</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07412271920802764</v>
+        <v>0.1116081643446868</v>
       </c>
       <c r="AC4">
-        <v>-0.07412271920802764</v>
+        <v>-0.1116081643446868</v>
       </c>
       <c r="AD4">
-        <v>81.5</v>
+        <v>119.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>81.5</v>
+        <v>119.9</v>
       </c>
       <c r="AG4">
-        <v>52.1</v>
+        <v>95.60000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.1422338568935428</v>
+        <v>0.2152989764769259</v>
       </c>
       <c r="AI4">
-        <v>0.1450952465729037</v>
+        <v>0.2070096685082873</v>
       </c>
       <c r="AJ4">
-        <v>0.09584253127299484</v>
+        <v>0.1794968081111528</v>
       </c>
       <c r="AK4">
-        <v>0.09787713695284615</v>
+        <v>0.172283294287259</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -957,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0767</v>
+        <v>0.0969</v>
       </c>
       <c r="E5">
-        <v>0.0919</v>
+        <v>0.142</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,82 +981,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>306.7</v>
+        <v>324.9</v>
       </c>
       <c r="L5">
-        <v>0.3779886615725906</v>
+        <v>0.3622073578595317</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>136.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1372983870967742</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4192059095106186</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>136.2</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.1372983870967742</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.4192059095106186</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>135.1</v>
+        <v>130.2</v>
       </c>
       <c r="V5">
-        <v>0.1047124476825298</v>
+        <v>0.13125</v>
       </c>
       <c r="W5">
-        <v>0.2448898115618013</v>
+        <v>0.2292548687552921</v>
       </c>
       <c r="X5">
-        <v>0.08056590429417054</v>
+        <v>0.1235513750295153</v>
       </c>
       <c r="Y5">
-        <v>0.1643239072676308</v>
+        <v>0.1057034937257768</v>
       </c>
       <c r="Z5">
-        <v>0.5791577444682369</v>
+        <v>0.5576277508392391</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07432896456346558</v>
+        <v>0.1124596777891335</v>
       </c>
       <c r="AC5">
-        <v>-0.07432896456346558</v>
+        <v>-0.1124596777891335</v>
       </c>
       <c r="AD5">
-        <v>319.2</v>
+        <v>341.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>319.2</v>
+        <v>341.3</v>
       </c>
       <c r="AG5">
-        <v>184.1</v>
+        <v>211.1</v>
       </c>
       <c r="AH5">
-        <v>0.1983347831489996</v>
+        <v>0.2559813995349884</v>
       </c>
       <c r="AI5">
-        <v>0.1766659287137481</v>
+        <v>0.1813014608233732</v>
       </c>
       <c r="AJ5">
-        <v>0.1248728209997965</v>
+        <v>0.1754633862521819</v>
       </c>
       <c r="AK5">
-        <v>0.1101274152060776</v>
+        <v>0.1204702391143069</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,10 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0274</v>
+        <v>0.102</v>
       </c>
       <c r="E6">
-        <v>0.0114</v>
+        <v>0.153</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1088,34 +1097,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.001046087684926403</v>
+        <v>0.0008094655126213606</v>
       </c>
       <c r="J6">
-        <v>0.0008722903099044195</v>
+        <v>0.0005961436512768141</v>
       </c>
       <c r="K6">
-        <v>47.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L6">
-        <v>0.2825698988697204</v>
+        <v>0.3330254041570438</v>
       </c>
       <c r="M6">
-        <v>21</v>
+        <v>42.9</v>
       </c>
       <c r="N6">
-        <v>0.06892024942566459</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="O6">
-        <v>0.4421052631578947</v>
+        <v>0.5950069348127601</v>
       </c>
       <c r="P6">
-        <v>21</v>
+        <v>42.9</v>
       </c>
       <c r="Q6">
-        <v>0.06892024942566459</v>
+        <v>0.1313131313131313</v>
       </c>
       <c r="R6">
-        <v>0.4421052631578947</v>
+        <v>0.5950069348127601</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>395.9</v>
+        <v>144.9</v>
       </c>
       <c r="V6">
-        <v>1.299310797505743</v>
+        <v>0.4435261707988981</v>
       </c>
       <c r="W6">
-        <v>0.09818106655642828</v>
+        <v>0.1453922161726154</v>
       </c>
       <c r="X6">
-        <v>0.08208783895422275</v>
+        <v>0.1199976285406962</v>
       </c>
       <c r="Y6">
-        <v>0.01609322760220552</v>
+        <v>0.02539458763191926</v>
       </c>
       <c r="Z6">
-        <v>1.678385691047145</v>
+        <v>0.6196004014673724</v>
       </c>
       <c r="AA6">
-        <v>0.001464039574582657</v>
+        <v>0.0003693708456633392</v>
       </c>
       <c r="AB6">
-        <v>0.07594289782577548</v>
+        <v>0.1132580925941122</v>
       </c>
       <c r="AC6">
-        <v>-0.07447885825119283</v>
+        <v>-0.1128887217484489</v>
       </c>
       <c r="AD6">
-        <v>86.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="AE6">
-        <v>0.3557633008193588</v>
+        <v>0.318753582587377</v>
       </c>
       <c r="AF6">
-        <v>87.25576330081937</v>
+        <v>88.11875358258737</v>
       </c>
       <c r="AG6">
-        <v>-308.6442366991806</v>
+        <v>-56.78124641741263</v>
       </c>
       <c r="AH6">
-        <v>0.2226163548814871</v>
+        <v>0.2124271210535894</v>
       </c>
       <c r="AI6">
-        <v>0.15560386359152</v>
+        <v>0.1515320925416599</v>
       </c>
       <c r="AJ6">
-        <v>78.25195601554479</v>
+        <v>-0.2103642139116474</v>
       </c>
       <c r="AK6">
-        <v>-1.872207744026421</v>
+        <v>-0.1300476581720449</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1181,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>351.8218623481782</v>
+        <v>367.3640167364017</v>
       </c>
       <c r="AP6">
-        <v>-1249.571808498707</v>
+        <v>-237.5784368929399</v>
       </c>
     </row>
     <row r="7">
@@ -1204,13 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0476</v>
+        <v>0.0968</v>
       </c>
       <c r="E7">
-        <v>0.00357</v>
+        <v>0.132</v>
       </c>
       <c r="F7">
-        <v>0.205</v>
+        <v>0.143</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.00960891315487869</v>
+        <v>0.007230896683821935</v>
       </c>
       <c r="J7">
-        <v>0.007150528880188948</v>
+        <v>0.005507815116188782</v>
       </c>
       <c r="K7">
-        <v>121.7</v>
+        <v>183.8</v>
       </c>
       <c r="L7">
-        <v>0.2691287041132243</v>
+        <v>0.3711631663974152</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1252,55 +1261,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>89.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V7">
-        <v>0.1333432657926102</v>
+        <v>0.1463998631776979</v>
       </c>
       <c r="W7">
-        <v>0.161042741828768</v>
+        <v>0.2136960818509476</v>
       </c>
       <c r="X7">
-        <v>0.09630318607157821</v>
+        <v>0.1376182736685</v>
       </c>
       <c r="Y7">
-        <v>0.0647395557571898</v>
+        <v>0.07607780818244753</v>
       </c>
       <c r="Z7">
-        <v>0.4467168864373993</v>
+        <v>0.4149849455483031</v>
       </c>
       <c r="AA7">
-        <v>0.00319426199773871</v>
+        <v>0.002285660356081722</v>
       </c>
       <c r="AB7">
-        <v>0.07771061101565299</v>
+        <v>0.1152564125587455</v>
       </c>
       <c r="AC7">
-        <v>-0.07451634901791428</v>
+        <v>-0.1129707522026638</v>
       </c>
       <c r="AD7">
-        <v>396.7</v>
+        <v>347.2</v>
       </c>
       <c r="AE7">
-        <v>39.77424735681929</v>
+        <v>25.99629981085689</v>
       </c>
       <c r="AF7">
-        <v>436.4742473568193</v>
+        <v>373.1962998108569</v>
       </c>
       <c r="AG7">
-        <v>346.9742473568193</v>
+        <v>287.5962998108569</v>
       </c>
       <c r="AH7">
-        <v>0.394045675791735</v>
+        <v>0.3895998970708489</v>
       </c>
       <c r="AI7">
-        <v>0.3358077360314068</v>
+        <v>0.3081220607007601</v>
       </c>
       <c r="AJ7">
-        <v>0.3407808125746301</v>
+        <v>0.3297002404724374</v>
       </c>
       <c r="AK7">
-        <v>0.2866905977009709</v>
+        <v>0.2555057260397747</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1309,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>32.2520325203252</v>
+        <v>39.54441913439636</v>
       </c>
       <c r="AP7">
-        <v>28.20928840299343</v>
+        <v>32.75584280305887</v>
       </c>
     </row>
     <row r="8">
@@ -1332,13 +1341,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.08259999999999999</v>
+        <v>0.152</v>
       </c>
       <c r="E8">
-        <v>0.09960000000000001</v>
-      </c>
-      <c r="F8">
-        <v>0.25</v>
+        <v>0.234</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1353,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>283.4</v>
+        <v>382.4</v>
       </c>
       <c r="L8">
-        <v>0.3598730158730158</v>
+        <v>0.3944708066845471</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1380,55 +1386,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>397.6</v>
+        <v>533.8</v>
       </c>
       <c r="V8">
-        <v>0.2261017912994029</v>
+        <v>0.3923269145965015</v>
       </c>
       <c r="W8">
-        <v>0.2354211663066955</v>
+        <v>0.2702855527283008</v>
       </c>
       <c r="X8">
-        <v>0.09084028036856996</v>
+        <v>0.1408746901754686</v>
       </c>
       <c r="Y8">
-        <v>0.1445808859381255</v>
+        <v>0.1294108625528322</v>
       </c>
       <c r="Z8">
-        <v>0.5427665586877112</v>
+        <v>0.5062669730520158</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07674115726781204</v>
+        <v>0.1157663694246068</v>
       </c>
       <c r="AC8">
-        <v>-0.07674115726781204</v>
+        <v>-0.1157663694246068</v>
       </c>
       <c r="AD8">
-        <v>897.6</v>
+        <v>961.1</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>897.6</v>
+        <v>961.1</v>
       </c>
       <c r="AG8">
-        <v>500</v>
+        <v>427.3000000000001</v>
       </c>
       <c r="AH8">
-        <v>0.3379390836188397</v>
+        <v>0.4139639057587113</v>
       </c>
       <c r="AI8">
-        <v>0.3778095799309706</v>
+        <v>0.4296763233190272</v>
       </c>
       <c r="AJ8">
-        <v>0.2213858755811379</v>
+        <v>0.2389954695452766</v>
       </c>
       <c r="AK8">
-        <v>0.2527550298250935</v>
+        <v>0.2509101585437464</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1445,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I&amp;M Holdings PLC (NASE:IMH)</t>
+          <t>I&amp;M Group PLC (NASE:IMH)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1454,10 +1460,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0602</v>
+        <v>0.116</v>
       </c>
       <c r="E9">
-        <v>0.0392</v>
+        <v>0.0872</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1472,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>82.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L9">
-        <v>0.3797526339899222</v>
+        <v>0.3276365152146727</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1499,55 +1505,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>39.4</v>
+        <v>43.5</v>
       </c>
       <c r="V9">
-        <v>0.127839065541856</v>
+        <v>0.1909569798068481</v>
       </c>
       <c r="W9">
-        <v>0.1488330341113106</v>
+        <v>0.1277218069548261</v>
       </c>
       <c r="X9">
-        <v>0.09420953707740401</v>
+        <v>0.1395496469617569</v>
       </c>
       <c r="Y9">
-        <v>0.05462349703390659</v>
+        <v>-0.01182784000693077</v>
       </c>
       <c r="Z9">
-        <v>0.3448657187993681</v>
+        <v>0.3156994341360705</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07735914075682865</v>
+        <v>0.1188183842748315</v>
       </c>
       <c r="AC9">
-        <v>-0.07735914075682865</v>
+        <v>-0.1188183842748315</v>
       </c>
       <c r="AD9">
-        <v>183.9</v>
+        <v>154.6</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>183.9</v>
+        <v>154.6</v>
       </c>
       <c r="AG9">
-        <v>144.5</v>
+        <v>111.1</v>
       </c>
       <c r="AH9">
-        <v>0.3737045315992684</v>
+        <v>0.4042887029288703</v>
       </c>
       <c r="AI9">
-        <v>0.219608311440172</v>
+        <v>0.2025946795963832</v>
       </c>
       <c r="AJ9">
-        <v>0.3191959354981224</v>
+        <v>0.3278253172027147</v>
       </c>
       <c r="AK9">
-        <v>0.181077694235589</v>
+        <v>0.1543913285158421</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1573,10 +1579,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0225</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="E10">
-        <v>0.0539</v>
+        <v>0.149</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1591,10 +1597,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>94.8</v>
+        <v>110.5</v>
       </c>
       <c r="L10">
-        <v>0.3315844700944386</v>
+        <v>0.3634868421052632</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1618,55 +1624,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>50.7</v>
+        <v>59.9</v>
       </c>
       <c r="V10">
-        <v>0.08916637354906788</v>
+        <v>0.1106595233696656</v>
       </c>
       <c r="W10">
-        <v>0.2306008270493797</v>
+        <v>0.2484262589928057</v>
       </c>
       <c r="X10">
-        <v>0.1082734088274743</v>
+        <v>0.1701582467323477</v>
       </c>
       <c r="Y10">
-        <v>0.1223274182219054</v>
+        <v>0.07826801226045807</v>
       </c>
       <c r="Z10">
-        <v>0.2877125893126698</v>
+        <v>0.3455330756990225</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07935035282834821</v>
+        <v>0.119006241150414</v>
       </c>
       <c r="AC10">
-        <v>-0.07935035282834821</v>
+        <v>-0.119006241150414</v>
       </c>
       <c r="AD10">
-        <v>544</v>
+        <v>713.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>544</v>
+        <v>713.9</v>
       </c>
       <c r="AG10">
-        <v>493.3</v>
+        <v>654</v>
       </c>
       <c r="AH10">
-        <v>0.4889448139493079</v>
+        <v>0.5687539834289357</v>
       </c>
       <c r="AI10">
-        <v>0.5239333525955889</v>
+        <v>0.5812571242468654</v>
       </c>
       <c r="AJ10">
-        <v>0.4645446840568792</v>
+        <v>0.5471429766585795</v>
       </c>
       <c r="AK10">
-        <v>0.4994937221547185</v>
+        <v>0.5597877257553711</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1692,10 +1698,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0189</v>
+        <v>0.0105</v>
       </c>
       <c r="E11">
-        <v>-0.0891</v>
+        <v>-0.07139999999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1710,10 +1716,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="L11">
-        <v>0.2191044776119403</v>
+        <v>0.2090956612650287</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1737,55 +1743,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="V11">
-        <v>0.4115646258503401</v>
+        <v>0.5392762577228597</v>
       </c>
       <c r="W11">
-        <v>0.06345089903181191</v>
+        <v>0.06549860815457671</v>
       </c>
       <c r="X11">
-        <v>0.1301583692571635</v>
+        <v>0.1993906046301315</v>
       </c>
       <c r="Y11">
-        <v>-0.06670747022535155</v>
+        <v>-0.1338919964755548</v>
       </c>
       <c r="Z11">
-        <v>0.2300824175824176</v>
+        <v>0.2479167476640359</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.08131595093950438</v>
+        <v>0.1208896096496279</v>
       </c>
       <c r="AC11">
-        <v>-0.08131595093950438</v>
+        <v>-0.1208896096496279</v>
       </c>
       <c r="AD11">
-        <v>223</v>
+        <v>218.7</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>223</v>
+        <v>218.7</v>
       </c>
       <c r="AG11">
-        <v>162.5</v>
+        <v>157.6</v>
       </c>
       <c r="AH11">
-        <v>0.6027027027027027</v>
+        <v>0.6587349397590361</v>
       </c>
       <c r="AI11">
-        <v>0.2485510477039679</v>
+        <v>0.2529786003470214</v>
       </c>
       <c r="AJ11">
-        <v>0.5250403877221325</v>
+        <v>0.581764488741233</v>
       </c>
       <c r="AK11">
-        <v>0.1942153699055814</v>
+        <v>0.1961662932536719</v>
       </c>
       <c r="AL11">
         <v>0</v>

--- a/research/traditional_assets/database/data/kenya/kenya_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/kenya/kenya_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0969</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="E2">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="F2">
-        <v>0.143</v>
+        <v>0.154</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0009489134761535918</v>
+        <v>0.001116100071962991</v>
       </c>
       <c r="J2">
-        <v>0.0006890208895808835</v>
+        <v>0.0008242395999965371</v>
       </c>
       <c r="K2">
-        <v>1424</v>
+        <v>1245.6</v>
       </c>
       <c r="L2">
-        <v>0.3597594866353393</v>
+        <v>0.3270493094575435</v>
       </c>
       <c r="M2">
-        <v>299.4939</v>
+        <v>227.6897</v>
       </c>
       <c r="N2">
-        <v>0.05862428797932938</v>
+        <v>0.06651758691206544</v>
       </c>
       <c r="O2">
-        <v>0.21031875</v>
+        <v>0.1827951991008349</v>
       </c>
       <c r="P2">
-        <v>299.4939</v>
+        <v>227.6897</v>
       </c>
       <c r="Q2">
-        <v>0.05862428797932938</v>
+        <v>0.06651758691206544</v>
       </c>
       <c r="R2">
-        <v>0.21031875</v>
+        <v>0.1827951991008349</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1168.4</v>
+        <v>1238.2</v>
       </c>
       <c r="V2">
-        <v>0.2287078904613698</v>
+        <v>0.3617294770669004</v>
       </c>
       <c r="W2">
-        <v>0.2027765470388421</v>
+        <v>0.1779694495654464</v>
       </c>
       <c r="X2">
-        <v>0.1376182736685</v>
+        <v>0.1241541480009149</v>
       </c>
       <c r="Y2">
-        <v>0.06515827337034208</v>
+        <v>0.05381530156453147</v>
       </c>
       <c r="Z2">
-        <v>0.4554500190354169</v>
+        <v>0.430993065722842</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1152564125587455</v>
+        <v>0.105457849918543</v>
       </c>
       <c r="AC2">
-        <v>-0.1129707522026638</v>
+        <v>-0.1049159447607844</v>
       </c>
       <c r="AD2">
-        <v>3076.9</v>
+        <v>2901.1</v>
       </c>
       <c r="AE2">
-        <v>26.31505339344426</v>
+        <v>20.34110632960877</v>
       </c>
       <c r="AF2">
-        <v>3103.215053393444</v>
+        <v>2921.441106329609</v>
       </c>
       <c r="AG2">
-        <v>1934.815053393444</v>
+        <v>1683.241106329609</v>
       </c>
       <c r="AH2">
-        <v>0.3778917625446076</v>
+        <v>0.4604725707698662</v>
       </c>
       <c r="AI2">
-        <v>0.305753093854989</v>
+        <v>0.3073570196749764</v>
       </c>
       <c r="AJ2">
-        <v>0.2746945294681075</v>
+        <v>0.3296438752653282</v>
       </c>
       <c r="AK2">
-        <v>0.215433894931774</v>
+        <v>0.2036135791990503</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>341.1575562700964</v>
+        <v>348.7318187282125</v>
       </c>
       <c r="AP2">
-        <v>214.526560970556</v>
+        <v>202.3369523175392</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.22</v>
+        <v>0.239</v>
       </c>
       <c r="E3">
-        <v>0.194</v>
+        <v>0.263</v>
+      </c>
+      <c r="F3">
+        <v>0.144</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>137.3</v>
+        <v>105.9</v>
       </c>
       <c r="L3">
-        <v>0.3545055512522592</v>
+        <v>0.3104661389621812</v>
       </c>
       <c r="M3">
-        <v>57.66250000000001</v>
+        <v>44.4825</v>
       </c>
       <c r="N3">
-        <v>0.1097706072720351</v>
+        <v>0.1086263736263736</v>
       </c>
       <c r="O3">
-        <v>0.4199745083758194</v>
+        <v>0.420042492917847</v>
       </c>
       <c r="P3">
-        <v>57.66250000000001</v>
+        <v>44.4825</v>
       </c>
       <c r="Q3">
-        <v>0.1097706072720351</v>
+        <v>0.1086263736263736</v>
       </c>
       <c r="R3">
-        <v>0.4199745083758194</v>
+        <v>0.420042492917847</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>85.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="V3">
-        <v>0.1620026651437274</v>
+        <v>0.231013431013431</v>
       </c>
       <c r="W3">
-        <v>0.2027765470388421</v>
+        <v>0.1581305061968045</v>
       </c>
       <c r="X3">
-        <v>0.1191524539314403</v>
+        <v>0.09683099769705303</v>
       </c>
       <c r="Y3">
-        <v>0.08362409310740182</v>
+        <v>0.06129950849975152</v>
       </c>
       <c r="Z3">
-        <v>0.5687224669603524</v>
+        <v>0.4757322175732218</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1113153141329352</v>
+        <v>0.09587802948186749</v>
       </c>
       <c r="AC3">
-        <v>-0.1113153141329352</v>
+        <v>-0.09587802948186749</v>
       </c>
       <c r="AD3">
-        <v>132.4</v>
+        <v>26.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>132.4</v>
+        <v>26.4</v>
       </c>
       <c r="AG3">
-        <v>47.30000000000001</v>
+        <v>-68.19999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.2013075870457656</v>
+        <v>0.06056434962147281</v>
       </c>
       <c r="AI3">
-        <v>0.1650049850448654</v>
+        <v>0.04234841193455245</v>
       </c>
       <c r="AJ3">
-        <v>0.08260565840027946</v>
+        <v>-0.1998242015821857</v>
       </c>
       <c r="AK3">
-        <v>0.06594172591663183</v>
+        <v>-0.1289712556732224</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,10 +844,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0697</v>
+        <v>0.066</v>
       </c>
       <c r="E4">
-        <v>0.136</v>
+        <v>0.0898</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>94.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="L4">
-        <v>0.3664596273291925</v>
+        <v>0.3634116192830655</v>
       </c>
       <c r="M4">
-        <v>62.7314</v>
+        <v>55.92919999999999</v>
       </c>
       <c r="N4">
-        <v>0.143550114416476</v>
+        <v>0.1431512669567443</v>
       </c>
       <c r="O4">
-        <v>0.6645275423728814</v>
+        <v>0.6341179138321995</v>
       </c>
       <c r="P4">
-        <v>62.7314</v>
+        <v>55.92919999999999</v>
       </c>
       <c r="Q4">
-        <v>0.143550114416476</v>
+        <v>0.1431512669567443</v>
       </c>
       <c r="R4">
-        <v>0.6645275423728814</v>
+        <v>0.6341179138321995</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -889,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>24.3</v>
+        <v>22.8</v>
       </c>
       <c r="V4">
-        <v>0.05560640732265446</v>
+        <v>0.05835679549526492</v>
       </c>
       <c r="W4">
-        <v>0.1965847563515202</v>
+        <v>0.1920313520574788</v>
       </c>
       <c r="X4">
-        <v>0.120219804859396</v>
+        <v>0.09688193400785231</v>
       </c>
       <c r="Y4">
-        <v>0.0763649514921242</v>
+        <v>0.09514941804962646</v>
       </c>
       <c r="Z4">
-        <v>0.4839376291564907</v>
+        <v>0.4373761038024868</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.1116081643446868</v>
+        <v>0.09590764595580489</v>
       </c>
       <c r="AC4">
-        <v>-0.1116081643446868</v>
+        <v>-0.09590764595580489</v>
       </c>
       <c r="AD4">
-        <v>119.9</v>
+        <v>25.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>119.9</v>
+        <v>25.7</v>
       </c>
       <c r="AG4">
-        <v>95.60000000000001</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.2152989764769259</v>
+        <v>0.0617195004803074</v>
       </c>
       <c r="AI4">
-        <v>0.2070096685082873</v>
+        <v>0.05997666277712952</v>
       </c>
       <c r="AJ4">
-        <v>0.1794968081111528</v>
+        <v>0.007367886178861785</v>
       </c>
       <c r="AK4">
-        <v>0.172283294287259</v>
+        <v>0.007148139018979538</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KCB Group PLC (NASE:KCB)</t>
+          <t>Stanbic Holdings Plc (NASE:SBIC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0969</v>
+        <v>0.0975</v>
       </c>
       <c r="E5">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +978,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.0005960223279631182</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.0004409907849359469</v>
       </c>
       <c r="K5">
-        <v>324.9</v>
+        <v>80.5</v>
       </c>
       <c r="L5">
-        <v>0.3622073578595317</v>
+        <v>0.3576188360728565</v>
       </c>
       <c r="M5">
-        <v>136.2</v>
+        <v>55.9</v>
       </c>
       <c r="N5">
-        <v>0.1372983870967742</v>
+        <v>0.2037172011661808</v>
       </c>
       <c r="O5">
-        <v>0.4192059095106186</v>
+        <v>0.6944099378881987</v>
       </c>
       <c r="P5">
-        <v>136.2</v>
+        <v>55.9</v>
       </c>
       <c r="Q5">
-        <v>0.1372983870967742</v>
+        <v>0.2037172011661808</v>
       </c>
       <c r="R5">
-        <v>0.4192059095106186</v>
+        <v>0.6944099378881987</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,61 +1014,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>130.2</v>
+        <v>139.4</v>
       </c>
       <c r="V5">
-        <v>0.13125</v>
+        <v>0.5080174927113703</v>
       </c>
       <c r="W5">
-        <v>0.2292548687552921</v>
+        <v>0.1631536278881232</v>
       </c>
       <c r="X5">
-        <v>0.1235513750295153</v>
+        <v>0.109286488292307</v>
       </c>
       <c r="Y5">
-        <v>0.1057034937257768</v>
+        <v>0.05386713959581628</v>
       </c>
       <c r="Z5">
-        <v>0.5576277508392391</v>
+        <v>0.6297839222049858</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.000277728906193216</v>
       </c>
       <c r="AB5">
-        <v>0.1124596777891335</v>
+        <v>0.1014512585327597</v>
       </c>
       <c r="AC5">
-        <v>-0.1124596777891335</v>
+        <v>-0.1011735296265665</v>
       </c>
       <c r="AD5">
-        <v>341.3</v>
+        <v>105.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.4241768698775105</v>
       </c>
       <c r="AF5">
-        <v>341.3</v>
+        <v>105.6241768698775</v>
       </c>
       <c r="AG5">
-        <v>211.1</v>
+        <v>-33.77582313012249</v>
       </c>
       <c r="AH5">
-        <v>0.2559813995349884</v>
+        <v>0.2779406766692211</v>
       </c>
       <c r="AI5">
-        <v>0.1813014608233732</v>
+        <v>0.1885054781321819</v>
       </c>
       <c r="AJ5">
-        <v>0.1754633862521819</v>
+        <v>-0.1403675373334886</v>
       </c>
       <c r="AK5">
-        <v>0.1204702391143069</v>
+        <v>-0.08024206017646686</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>480.365296803653</v>
+      </c>
+      <c r="AP5">
+        <v>-154.2275028772716</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stanbic Holdings Plc (NASE:SBIC)</t>
+          <t>I&amp;M Group PLC (NASE:IMH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,10 +1094,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.102</v>
+        <v>0.134</v>
       </c>
       <c r="E6">
-        <v>0.153</v>
+        <v>0.0944</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1097,103 +1106,94 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0008094655126213606</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.0005961436512768141</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>72.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="L6">
-        <v>0.3330254041570438</v>
+        <v>0.3612334801762114</v>
       </c>
       <c r="M6">
-        <v>42.9</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.1313131313131313</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5950069348127601</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>42.9</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.1313131313131313</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.5950069348127601</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>144.9</v>
+        <v>48.3</v>
       </c>
       <c r="V6">
-        <v>0.4435261707988981</v>
+        <v>0.2615051434759069</v>
       </c>
       <c r="W6">
-        <v>0.1453922161726154</v>
+        <v>0.1446973707428975</v>
       </c>
       <c r="X6">
-        <v>0.1199976285406962</v>
+        <v>0.1209875810541105</v>
       </c>
       <c r="Y6">
-        <v>0.02539458763191926</v>
+        <v>0.02370978968878699</v>
       </c>
       <c r="Z6">
-        <v>0.6196004014673724</v>
+        <v>0.3349070522277958</v>
       </c>
       <c r="AA6">
-        <v>0.0003693708456633392</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.1132580925941122</v>
+        <v>0.1047568846146709</v>
       </c>
       <c r="AC6">
-        <v>-0.1128887217484489</v>
+        <v>-0.1047568846146709</v>
       </c>
       <c r="AD6">
-        <v>87.8</v>
+        <v>126.7</v>
       </c>
       <c r="AE6">
-        <v>0.318753582587377</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>88.11875358258737</v>
+        <v>126.7</v>
       </c>
       <c r="AG6">
-        <v>-56.78124641741263</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.2124271210535894</v>
+        <v>0.4068721901091844</v>
       </c>
       <c r="AI6">
-        <v>0.1515320925416599</v>
+        <v>0.1805357651752636</v>
       </c>
       <c r="AJ6">
-        <v>-0.2103642139116474</v>
+        <v>0.2979855568225009</v>
       </c>
       <c r="AK6">
-        <v>-0.1300476581720449</v>
+        <v>0.1199693955623566</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>367.3640167364017</v>
-      </c>
-      <c r="AP6">
-        <v>-237.5784368929399</v>
       </c>
     </row>
     <row r="7">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0968</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="E7">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="F7">
-        <v>0.143</v>
+        <v>0.119</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1228,16 +1228,16 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.007230896683821935</v>
+        <v>0.009392229313378389</v>
       </c>
       <c r="J7">
-        <v>0.005507815116188782</v>
+        <v>0.006983169078534523</v>
       </c>
       <c r="K7">
-        <v>183.8</v>
+        <v>156</v>
       </c>
       <c r="L7">
-        <v>0.3711631663974152</v>
+        <v>0.3559206023271732</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1261,55 +1261,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>85.59999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="V7">
-        <v>0.1463998631776979</v>
+        <v>0.1862262825017569</v>
       </c>
       <c r="W7">
-        <v>0.2136960818509476</v>
+        <v>0.1867592481743086</v>
       </c>
       <c r="X7">
-        <v>0.1376182736685</v>
+        <v>0.1364265987373416</v>
       </c>
       <c r="Y7">
-        <v>0.07607780818244753</v>
+        <v>0.050332649436967</v>
       </c>
       <c r="Z7">
-        <v>0.4149849455483031</v>
+        <v>0.392454652538291</v>
       </c>
       <c r="AA7">
-        <v>0.002285660356081722</v>
+        <v>0.002740577194332404</v>
       </c>
       <c r="AB7">
-        <v>0.1152564125587455</v>
+        <v>0.1076565219551168</v>
       </c>
       <c r="AC7">
-        <v>-0.1129707522026638</v>
+        <v>-0.1049159447607844</v>
       </c>
       <c r="AD7">
-        <v>347.2</v>
+        <v>442.5</v>
       </c>
       <c r="AE7">
-        <v>25.99629981085689</v>
+        <v>19.91692945973126</v>
       </c>
       <c r="AF7">
-        <v>373.1962998108569</v>
+        <v>462.4169294597313</v>
       </c>
       <c r="AG7">
-        <v>287.5962998108569</v>
+        <v>382.9169294597313</v>
       </c>
       <c r="AH7">
-        <v>0.3895998970708489</v>
+        <v>0.5199686570013393</v>
       </c>
       <c r="AI7">
-        <v>0.3081220607007601</v>
+        <v>0.388058375160369</v>
       </c>
       <c r="AJ7">
-        <v>0.3297002404724374</v>
+        <v>0.4728438188062998</v>
       </c>
       <c r="AK7">
-        <v>0.2555057260397747</v>
+        <v>0.3443135513149261</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1318,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>39.54441913439636</v>
+        <v>54.62962962962963</v>
       </c>
       <c r="AP7">
-        <v>32.75584280305887</v>
+        <v>47.27369499502855</v>
       </c>
     </row>
     <row r="8">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equity Group Holdings Plc (NASE:EQTY)</t>
+          <t>Absa Bank Kenya PLC (NASE:ABSA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.152</v>
+        <v>0.0978</v>
       </c>
       <c r="E8">
-        <v>0.234</v>
+        <v>0.181</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,82 +1359,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>382.4</v>
+        <v>109.1</v>
       </c>
       <c r="L8">
-        <v>0.3944708066845471</v>
+        <v>0.3636666666666666</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>48.8835</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.1231632653061225</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.4480614115490376</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>48.8835</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.1231632653061225</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.4480614115490376</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>533.8</v>
+        <v>61.7</v>
       </c>
       <c r="V8">
-        <v>0.3923269145965015</v>
+        <v>0.1554547745023936</v>
       </c>
       <c r="W8">
-        <v>0.2702855527283008</v>
+        <v>0.2186810984165163</v>
       </c>
       <c r="X8">
-        <v>0.1408746901754686</v>
+        <v>0.1241541480009149</v>
       </c>
       <c r="Y8">
-        <v>0.1294108625528322</v>
+        <v>0.0945269504156014</v>
       </c>
       <c r="Z8">
-        <v>0.5062669730520158</v>
+        <v>0.2311604253351827</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.1157663694246068</v>
+        <v>0.105457849918543</v>
       </c>
       <c r="AC8">
-        <v>-0.1157663694246068</v>
+        <v>-0.105457849918543</v>
       </c>
       <c r="AD8">
-        <v>961.1</v>
+        <v>304.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>961.1</v>
+        <v>304.6</v>
       </c>
       <c r="AG8">
-        <v>427.3000000000001</v>
+        <v>242.9</v>
       </c>
       <c r="AH8">
-        <v>0.4139639057587113</v>
+        <v>0.4342124019957235</v>
       </c>
       <c r="AI8">
-        <v>0.4296763233190272</v>
+        <v>0.4088041873574017</v>
       </c>
       <c r="AJ8">
-        <v>0.2389954695452766</v>
+        <v>0.3796498905908097</v>
       </c>
       <c r="AK8">
-        <v>0.2509101585437464</v>
+        <v>0.355428738659643</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>I&amp;M Group PLC (NASE:IMH)</t>
+          <t>Equity Group Holdings Plc (NASE:EQTY)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,10 +1463,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.116</v>
+        <v>0.182</v>
       </c>
       <c r="E9">
-        <v>0.0872</v>
+        <v>0.182</v>
+      </c>
+      <c r="F9">
+        <v>0.281</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>78.59999999999999</v>
+        <v>311.1</v>
       </c>
       <c r="L9">
-        <v>0.3276365152146727</v>
+        <v>0.3287540948959105</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1505,55 +1511,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>43.5</v>
+        <v>511.6</v>
       </c>
       <c r="V9">
-        <v>0.1909569798068481</v>
+        <v>0.6312931885488648</v>
       </c>
       <c r="W9">
-        <v>0.1277218069548261</v>
+        <v>0.2547285679194302</v>
       </c>
       <c r="X9">
-        <v>0.1395496469617569</v>
+        <v>0.1385789441327213</v>
       </c>
       <c r="Y9">
-        <v>-0.01182784000693077</v>
+        <v>0.1161496237867089</v>
       </c>
       <c r="Z9">
-        <v>0.3156994341360705</v>
+        <v>0.5740021836709935</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.1188183842748315</v>
+        <v>0.1079752083384717</v>
       </c>
       <c r="AC9">
-        <v>-0.1188183842748315</v>
+        <v>-0.1079752083384717</v>
       </c>
       <c r="AD9">
-        <v>154.6</v>
+        <v>922.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>154.6</v>
+        <v>922.7</v>
       </c>
       <c r="AG9">
-        <v>111.1</v>
+        <v>411.1</v>
       </c>
       <c r="AH9">
-        <v>0.4042887029288703</v>
+        <v>0.5323985921181698</v>
       </c>
       <c r="AI9">
-        <v>0.2025946795963832</v>
+        <v>0.4145475783987779</v>
       </c>
       <c r="AJ9">
-        <v>0.3278253172027147</v>
+        <v>0.3365534179287761</v>
       </c>
       <c r="AK9">
-        <v>0.1543913285158421</v>
+        <v>0.2398203243495509</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1570,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Absa Bank Kenya PLC (NASE:ABSA)</t>
+          <t>KCB Group PLC (NASE:KCB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1579,10 +1585,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.06559999999999999</v>
+        <v>0.144</v>
       </c>
       <c r="E10">
-        <v>0.149</v>
+        <v>0.121</v>
+      </c>
+      <c r="F10">
+        <v>0.154</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1597,82 +1606,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>110.5</v>
+        <v>270.3</v>
       </c>
       <c r="L10">
-        <v>0.3634868421052632</v>
+        <v>0.3015058561070831</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>22.4945</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.05008795368514807</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.083220495745468</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>22.4945</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.05008795368514807</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.083220495745468</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>59.9</v>
+        <v>222.2</v>
       </c>
       <c r="V10">
-        <v>0.1106595233696656</v>
+        <v>0.4947673124025829</v>
       </c>
       <c r="W10">
-        <v>0.2484262589928057</v>
+        <v>0.1779694495654464</v>
       </c>
       <c r="X10">
-        <v>0.1701582467323477</v>
+        <v>0.1569583603022623</v>
       </c>
       <c r="Y10">
-        <v>0.07826801226045807</v>
+        <v>0.0210110892631841</v>
       </c>
       <c r="Z10">
-        <v>0.3455330756990225</v>
+        <v>0.5182380484421065</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.119006241150414</v>
+        <v>0.1126565616801762</v>
       </c>
       <c r="AC10">
-        <v>-0.119006241150414</v>
+        <v>-0.1126565616801762</v>
       </c>
       <c r="AD10">
-        <v>713.9</v>
+        <v>723.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>713.9</v>
+        <v>723.7</v>
       </c>
       <c r="AG10">
-        <v>654</v>
+        <v>501.5000000000001</v>
       </c>
       <c r="AH10">
-        <v>0.5687539834289357</v>
+        <v>0.6170702592087312</v>
       </c>
       <c r="AI10">
-        <v>0.5812571242468654</v>
+        <v>0.3218447033709864</v>
       </c>
       <c r="AJ10">
-        <v>0.5471429766585795</v>
+        <v>0.5275615400799495</v>
       </c>
       <c r="AK10">
-        <v>0.5597877257553711</v>
+        <v>0.2474832214765101</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1698,10 +1710,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0105</v>
+        <v>0.0457</v>
       </c>
       <c r="E11">
-        <v>-0.07139999999999999</v>
+        <v>-0.0195</v>
+      </c>
+      <c r="F11">
+        <v>0.269</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,10 +1731,10 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="L11">
-        <v>0.2090956612650287</v>
+        <v>0.2218162839248434</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1743,55 +1758,55 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>61.1</v>
+        <v>58.1</v>
       </c>
       <c r="V11">
-        <v>0.5392762577228597</v>
+        <v>0.722636815920398</v>
       </c>
       <c r="W11">
-        <v>0.06549860815457671</v>
+        <v>0.07322536181943487</v>
       </c>
       <c r="X11">
-        <v>0.1993906046301315</v>
+        <v>0.2024199080044595</v>
       </c>
       <c r="Y11">
-        <v>-0.1338919964755548</v>
+        <v>-0.1291945461850246</v>
       </c>
       <c r="Z11">
-        <v>0.2479167476640359</v>
+        <v>0.2601281633539699</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.1208896096496279</v>
+        <v>0.1131831228615552</v>
       </c>
       <c r="AC11">
-        <v>-0.1208896096496279</v>
+        <v>-0.1131831228615552</v>
       </c>
       <c r="AD11">
-        <v>218.7</v>
+        <v>223.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>218.7</v>
+        <v>223.6</v>
       </c>
       <c r="AG11">
-        <v>157.6</v>
+        <v>165.5</v>
       </c>
       <c r="AH11">
-        <v>0.6587349397590361</v>
+        <v>0.7355263157894737</v>
       </c>
       <c r="AI11">
-        <v>0.2529786003470214</v>
+        <v>0.2867034235158354</v>
       </c>
       <c r="AJ11">
-        <v>0.581764488741233</v>
+        <v>0.673037820252135</v>
       </c>
       <c r="AK11">
-        <v>0.1961662932536719</v>
+        <v>0.2292878913826545</v>
       </c>
       <c r="AL11">
         <v>0</v>
